--- a/NHS consultancies mapping.xlsx.xlsx
+++ b/NHS consultancies mapping.xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NM2.WQGISDUV\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F9330E-6C61-4776-A964-4332058C38E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D611AA-530C-4ABB-9131-F1D0B33AC521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7340E7F6-9FC5-4620-8510-CFC58B28CD68}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7340E7F6-9FC5-4620-8510-CFC58B28CD68}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="1" r:id="rId1"/>
@@ -132,9 +132,6 @@
     <t>Capability</t>
   </si>
   <si>
-    <t>Strategy &amp; Advisory</t>
-  </si>
-  <si>
     <t>Corporate strategy development/review</t>
   </si>
   <si>
@@ -153,9 +150,6 @@
     <t>Governance/assurance review</t>
   </si>
   <si>
-    <t>Transformation &amp; Change</t>
-  </si>
-  <si>
     <t>Establish new services/pilots</t>
   </si>
   <si>
@@ -171,9 +165,6 @@
     <t>Flow improvement</t>
   </si>
   <si>
-    <t>Quality Improvement</t>
-  </si>
-  <si>
     <t>Blended QI - accredited individuals</t>
   </si>
   <si>
@@ -183,12 +174,6 @@
     <t>PDSA/IHI</t>
   </si>
   <si>
-    <t>After ACtion Review (AAR)</t>
-  </si>
-  <si>
-    <t>OD and leadership development</t>
-  </si>
-  <si>
     <t>Team development</t>
   </si>
   <si>
@@ -216,30 +201,15 @@
     <t>Well-led reviews/Board advisory, support and investigations</t>
   </si>
   <si>
-    <t>Analytics and evaluation</t>
-  </si>
-  <si>
     <t>Analytical research, modelling and insight (incl Demand &amp; Capacity and simulation)</t>
   </si>
   <si>
-    <t>Analytical product devpt (e.g. dashboards)</t>
-  </si>
-  <si>
-    <t>Digital and automation</t>
-  </si>
-  <si>
     <t>Digital enablement, maturity, inclusion</t>
   </si>
   <si>
-    <t>PMO and delivery support</t>
-  </si>
-  <si>
     <t>Project and Programme Management (PPM)</t>
   </si>
   <si>
-    <t>Clinical Service Redesign</t>
-  </si>
-  <si>
     <t>Clinical Strategy</t>
   </si>
   <si>
@@ -252,9 +222,6 @@
     <t>Clinical/medical workforce engagement</t>
   </si>
   <si>
-    <t>Finance &amp; Corporate</t>
-  </si>
-  <si>
     <t>Audit and risk advisory/delivery</t>
   </si>
   <si>
@@ -264,9 +231,6 @@
     <t>Back-office managed services</t>
   </si>
   <si>
-    <t>Engagement/ consultation</t>
-  </si>
-  <si>
     <t>Strategic communications advisory</t>
   </si>
   <si>
@@ -361,6 +325,42 @@
   </si>
   <si>
     <t>Interims</t>
+  </si>
+  <si>
+    <t>OD &amp; leadership development</t>
+  </si>
+  <si>
+    <t>Analytics &amp; evaluation</t>
+  </si>
+  <si>
+    <t>Digital &amp; automation</t>
+  </si>
+  <si>
+    <t>PMO &amp; delivery support</t>
+  </si>
+  <si>
+    <t>Clinical service redesign</t>
+  </si>
+  <si>
+    <t>Engagement &amp; consultation</t>
+  </si>
+  <si>
+    <t>Finance &amp; corporate</t>
+  </si>
+  <si>
+    <t>Transformation &amp; change</t>
+  </si>
+  <si>
+    <t>Strategy &amp; advisory</t>
+  </si>
+  <si>
+    <t>Quality improvement</t>
+  </si>
+  <si>
+    <t>After Action Review (AAR)</t>
+  </si>
+  <si>
+    <t>Analytical product development (e.g. dashboards)</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +1009,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1046,7 +1046,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1060,7 +1060,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1074,7 +1074,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="5" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1100,7 +1100,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1114,7 +1114,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1128,7 +1128,7 @@
         <v>17</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1142,7 +1142,7 @@
         <v>19</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1156,7 +1156,7 @@
         <v>21</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1170,7 +1170,7 @@
         <v>23</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1184,7 +1184,7 @@
         <v>25</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1222,7 +1222,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1242,10 +1242,10 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1256,10 +1256,10 @@
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1270,10 +1270,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1284,10 +1284,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1298,10 +1298,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1312,10 +1312,10 @@
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1326,10 +1326,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1340,10 +1340,10 @@
         <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1354,10 +1354,10 @@
         <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1368,10 +1368,10 @@
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1382,10 +1382,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1396,10 +1396,10 @@
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1410,10 +1410,10 @@
         <v>3</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1424,10 +1424,10 @@
         <v>3</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1438,10 +1438,10 @@
         <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1452,10 +1452,10 @@
         <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1466,10 +1466,10 @@
         <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1480,10 +1480,10 @@
         <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1494,10 +1494,10 @@
         <v>3</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1508,10 +1508,10 @@
         <v>3</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1522,10 +1522,10 @@
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1536,10 +1536,10 @@
         <v>3</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1550,10 +1550,10 @@
         <v>3</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1564,10 +1564,10 @@
         <v>3</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1578,10 +1578,10 @@
         <v>3</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1592,10 +1592,10 @@
         <v>3</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1606,10 +1606,10 @@
         <v>3</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1620,10 +1620,10 @@
         <v>3</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1634,10 +1634,10 @@
         <v>3</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1648,10 +1648,10 @@
         <v>3</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1662,10 +1662,10 @@
         <v>3</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1676,10 +1676,10 @@
         <v>3</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1690,10 +1690,10 @@
         <v>3</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1704,10 +1704,10 @@
         <v>3</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1718,10 +1718,10 @@
         <v>3</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1732,10 +1732,10 @@
         <v>3</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1746,10 +1746,10 @@
         <v>3</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1760,10 +1760,10 @@
         <v>3</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1774,10 +1774,10 @@
         <v>3</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1788,10 +1788,10 @@
         <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1802,10 +1802,10 @@
         <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1816,10 +1816,10 @@
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1830,10 +1830,10 @@
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1844,10 +1844,10 @@
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1858,10 +1858,10 @@
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1872,10 +1872,10 @@
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1886,10 +1886,10 @@
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1900,10 +1900,10 @@
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1914,10 +1914,10 @@
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1928,10 +1928,10 @@
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1942,10 +1942,10 @@
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1956,10 +1956,10 @@
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1970,10 +1970,10 @@
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1984,10 +1984,10 @@
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1998,10 +1998,10 @@
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -2012,10 +2012,10 @@
         <v>9</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -2026,10 +2026,10 @@
         <v>9</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -2040,10 +2040,10 @@
         <v>9</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2054,10 +2054,10 @@
         <v>9</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -2068,10 +2068,10 @@
         <v>9</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -2082,10 +2082,10 @@
         <v>9</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -2096,10 +2096,10 @@
         <v>9</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -2110,10 +2110,10 @@
         <v>9</v>
       </c>
       <c r="C64" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -2124,10 +2124,10 @@
         <v>9</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -2138,10 +2138,10 @@
         <v>9</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -2152,10 +2152,10 @@
         <v>9</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -2166,10 +2166,10 @@
         <v>9</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -2180,10 +2180,10 @@
         <v>9</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -2194,10 +2194,10 @@
         <v>9</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -2208,10 +2208,10 @@
         <v>9</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -2222,10 +2222,10 @@
         <v>9</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -2236,10 +2236,10 @@
         <v>9</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -2250,10 +2250,10 @@
         <v>9</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -2264,10 +2264,10 @@
         <v>9</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -2278,10 +2278,10 @@
         <v>9</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -2292,10 +2292,10 @@
         <v>9</v>
       </c>
       <c r="C77" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -2306,10 +2306,10 @@
         <v>9</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -2320,10 +2320,10 @@
         <v>9</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -2334,10 +2334,10 @@
         <v>9</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -2348,10 +2348,10 @@
         <v>9</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -2362,10 +2362,10 @@
         <v>9</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -2376,10 +2376,10 @@
         <v>9</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -2390,10 +2390,10 @@
         <v>9</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -2404,10 +2404,10 @@
         <v>9</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -2418,10 +2418,10 @@
         <v>9</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -2432,10 +2432,10 @@
         <v>9</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -2446,10 +2446,10 @@
         <v>9</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -2460,10 +2460,10 @@
         <v>9</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -2474,10 +2474,10 @@
         <v>9</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -2488,10 +2488,10 @@
         <v>9</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -2502,10 +2502,10 @@
         <v>9</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -2516,10 +2516,10 @@
         <v>9</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -2530,10 +2530,10 @@
         <v>9</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -2544,10 +2544,10 @@
         <v>9</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -2558,10 +2558,10 @@
         <v>9</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -2572,10 +2572,10 @@
         <v>9</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -2586,10 +2586,10 @@
         <v>9</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -2600,10 +2600,10 @@
         <v>9</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -2614,10 +2614,10 @@
         <v>9</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -2628,10 +2628,10 @@
         <v>9</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -2642,10 +2642,10 @@
         <v>9</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -2656,10 +2656,10 @@
         <v>9</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -2670,10 +2670,10 @@
         <v>9</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -2684,10 +2684,10 @@
         <v>9</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -2698,10 +2698,10 @@
         <v>9</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -2712,10 +2712,10 @@
         <v>9</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -2726,10 +2726,10 @@
         <v>9</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -2740,10 +2740,10 @@
         <v>9</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -2754,10 +2754,10 @@
         <v>9</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -2768,10 +2768,10 @@
         <v>11</v>
       </c>
       <c r="C111" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D111" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -2782,10 +2782,10 @@
         <v>11</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -2796,10 +2796,10 @@
         <v>11</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -2810,10 +2810,10 @@
         <v>11</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -2824,10 +2824,10 @@
         <v>11</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -2838,10 +2838,10 @@
         <v>11</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -2852,10 +2852,10 @@
         <v>11</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -2866,10 +2866,10 @@
         <v>11</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -2880,10 +2880,10 @@
         <v>11</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -2894,10 +2894,10 @@
         <v>11</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -2908,10 +2908,10 @@
         <v>11</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -2922,10 +2922,10 @@
         <v>11</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -2936,10 +2936,10 @@
         <v>11</v>
       </c>
       <c r="C123" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D123" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
@@ -2950,10 +2950,10 @@
         <v>11</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
@@ -2964,10 +2964,10 @@
         <v>11</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
@@ -2978,10 +2978,10 @@
         <v>11</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
@@ -2992,10 +2992,10 @@
         <v>11</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
@@ -3006,10 +3006,10 @@
         <v>11</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
@@ -3020,10 +3020,10 @@
         <v>11</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
@@ -3034,10 +3034,10 @@
         <v>11</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
@@ -3048,10 +3048,10 @@
         <v>11</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
@@ -3062,10 +3062,10 @@
         <v>11</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
@@ -3076,10 +3076,10 @@
         <v>11</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
@@ -3090,10 +3090,10 @@
         <v>11</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
@@ -3104,10 +3104,10 @@
         <v>12</v>
       </c>
       <c r="C135" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D135" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
@@ -3118,10 +3118,10 @@
         <v>12</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
@@ -3132,10 +3132,10 @@
         <v>12</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
@@ -3146,10 +3146,10 @@
         <v>12</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
@@ -3160,10 +3160,10 @@
         <v>12</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
@@ -3174,10 +3174,10 @@
         <v>12</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
@@ -3188,10 +3188,10 @@
         <v>12</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
@@ -3202,10 +3202,10 @@
         <v>12</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
@@ -3216,10 +3216,10 @@
         <v>12</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -3230,10 +3230,10 @@
         <v>12</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -3244,10 +3244,10 @@
         <v>12</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
@@ -3258,10 +3258,10 @@
         <v>12</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
@@ -3272,10 +3272,10 @@
         <v>12</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
@@ -3286,10 +3286,10 @@
         <v>12</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
@@ -3300,10 +3300,10 @@
         <v>14</v>
       </c>
       <c r="C149" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D149" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
@@ -3314,10 +3314,10 @@
         <v>14</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
@@ -3328,10 +3328,10 @@
         <v>14</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
@@ -3342,10 +3342,10 @@
         <v>14</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
@@ -3356,10 +3356,10 @@
         <v>14</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
@@ -3370,10 +3370,10 @@
         <v>14</v>
       </c>
       <c r="C154" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D154" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
@@ -3384,10 +3384,10 @@
         <v>14</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
@@ -3398,10 +3398,10 @@
         <v>14</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
@@ -3412,10 +3412,10 @@
         <v>14</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
@@ -3426,10 +3426,10 @@
         <v>14</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
@@ -3440,10 +3440,10 @@
         <v>14</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
@@ -3454,10 +3454,10 @@
         <v>14</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
@@ -3468,10 +3468,10 @@
         <v>14</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
@@ -3482,10 +3482,10 @@
         <v>14</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -3496,10 +3496,10 @@
         <v>14</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
@@ -3510,10 +3510,10 @@
         <v>14</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
@@ -3524,10 +3524,10 @@
         <v>14</v>
       </c>
       <c r="C165" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D165" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
@@ -3538,10 +3538,10 @@
         <v>14</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
@@ -3552,10 +3552,10 @@
         <v>14</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
@@ -3566,10 +3566,10 @@
         <v>14</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
@@ -3580,10 +3580,10 @@
         <v>14</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
@@ -3594,10 +3594,10 @@
         <v>14</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
@@ -3608,10 +3608,10 @@
         <v>14</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
@@ -3622,10 +3622,10 @@
         <v>14</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
@@ -3636,10 +3636,10 @@
         <v>16</v>
       </c>
       <c r="C173" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D173" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
@@ -3650,10 +3650,10 @@
         <v>16</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
@@ -3664,10 +3664,10 @@
         <v>16</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
@@ -3678,10 +3678,10 @@
         <v>16</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
@@ -3692,10 +3692,10 @@
         <v>16</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
@@ -3706,10 +3706,10 @@
         <v>16</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
@@ -3720,10 +3720,10 @@
         <v>16</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
@@ -3734,10 +3734,10 @@
         <v>16</v>
       </c>
       <c r="C180" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D180" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
@@ -3748,10 +3748,10 @@
         <v>16</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
@@ -3762,10 +3762,10 @@
         <v>16</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
@@ -3776,10 +3776,10 @@
         <v>16</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
@@ -3790,10 +3790,10 @@
         <v>16</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
@@ -3804,10 +3804,10 @@
         <v>16</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
@@ -3818,10 +3818,10 @@
         <v>16</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
@@ -3832,10 +3832,10 @@
         <v>16</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
@@ -3846,10 +3846,10 @@
         <v>16</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
@@ -3860,10 +3860,10 @@
         <v>16</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
@@ -3874,10 +3874,10 @@
         <v>16</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
@@ -3888,10 +3888,10 @@
         <v>16</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
@@ -3902,10 +3902,10 @@
         <v>16</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
@@ -3916,10 +3916,10 @@
         <v>16</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
@@ -3930,10 +3930,10 @@
         <v>16</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
@@ -3944,10 +3944,10 @@
         <v>16</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
@@ -3958,10 +3958,10 @@
         <v>18</v>
       </c>
       <c r="C196" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D196" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D196" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
@@ -3972,10 +3972,10 @@
         <v>18</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
@@ -3986,10 +3986,10 @@
         <v>18</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
@@ -4000,10 +4000,10 @@
         <v>18</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
@@ -4014,10 +4014,10 @@
         <v>18</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
@@ -4028,10 +4028,10 @@
         <v>18</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
@@ -4042,10 +4042,10 @@
         <v>18</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
@@ -4056,10 +4056,10 @@
         <v>18</v>
       </c>
       <c r="C203" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D203" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
@@ -4070,10 +4070,10 @@
         <v>18</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
@@ -4084,10 +4084,10 @@
         <v>18</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
@@ -4098,10 +4098,10 @@
         <v>18</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
@@ -4112,10 +4112,10 @@
         <v>18</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
@@ -4126,10 +4126,10 @@
         <v>18</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
@@ -4140,10 +4140,10 @@
         <v>18</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
@@ -4154,10 +4154,10 @@
         <v>18</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
@@ -4168,10 +4168,10 @@
         <v>18</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
@@ -4182,10 +4182,10 @@
         <v>18</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
@@ -4196,10 +4196,10 @@
         <v>18</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
@@ -4210,10 +4210,10 @@
         <v>18</v>
       </c>
       <c r="C214" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D214" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="D214" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
@@ -4224,10 +4224,10 @@
         <v>18</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
@@ -4238,10 +4238,10 @@
         <v>18</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
@@ -4252,10 +4252,10 @@
         <v>18</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
@@ -4266,10 +4266,10 @@
         <v>18</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
@@ -4280,10 +4280,10 @@
         <v>18</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -4294,10 +4294,10 @@
         <v>18</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
@@ -4308,10 +4308,10 @@
         <v>18</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -4322,10 +4322,10 @@
         <v>18</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
@@ -4336,10 +4336,10 @@
         <v>18</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
@@ -4350,10 +4350,10 @@
         <v>18</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
@@ -4364,10 +4364,10 @@
         <v>18</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
@@ -4378,10 +4378,10 @@
         <v>18</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
@@ -4392,10 +4392,10 @@
         <v>18</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
@@ -4406,10 +4406,10 @@
         <v>18</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
@@ -4420,10 +4420,10 @@
         <v>18</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
@@ -4434,10 +4434,10 @@
         <v>18</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -4448,10 +4448,10 @@
         <v>18</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
@@ -4462,10 +4462,10 @@
         <v>18</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
@@ -4476,10 +4476,10 @@
         <v>18</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
@@ -4490,10 +4490,10 @@
         <v>18</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
@@ -4504,10 +4504,10 @@
         <v>18</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
@@ -4518,10 +4518,10 @@
         <v>18</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
@@ -4532,10 +4532,10 @@
         <v>18</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
@@ -4546,10 +4546,10 @@
         <v>18</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
@@ -4560,10 +4560,10 @@
         <v>20</v>
       </c>
       <c r="C239" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D239" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D239" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
@@ -4574,10 +4574,10 @@
         <v>20</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
@@ -4588,10 +4588,10 @@
         <v>20</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
@@ -4602,10 +4602,10 @@
         <v>20</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
@@ -4616,10 +4616,10 @@
         <v>20</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -4630,10 +4630,10 @@
         <v>20</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
@@ -4644,10 +4644,10 @@
         <v>20</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
@@ -4658,10 +4658,10 @@
         <v>20</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
@@ -4672,10 +4672,10 @@
         <v>20</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
@@ -4686,10 +4686,10 @@
         <v>20</v>
       </c>
       <c r="C248" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D248" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="D248" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
@@ -4700,10 +4700,10 @@
         <v>20</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
@@ -4714,10 +4714,10 @@
         <v>20</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
@@ -4728,10 +4728,10 @@
         <v>20</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
@@ -4742,10 +4742,10 @@
         <v>20</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
@@ -4756,10 +4756,10 @@
         <v>20</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
@@ -4770,10 +4770,10 @@
         <v>20</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
@@ -4784,10 +4784,10 @@
         <v>20</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
@@ -4798,10 +4798,10 @@
         <v>20</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
@@ -4812,10 +4812,10 @@
         <v>20</v>
       </c>
       <c r="C257" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D257" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="D257" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -4826,10 +4826,10 @@
         <v>20</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -4840,10 +4840,10 @@
         <v>20</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
@@ -4854,10 +4854,10 @@
         <v>20</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
@@ -4868,10 +4868,10 @@
         <v>20</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
@@ -4882,10 +4882,10 @@
         <v>20</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
@@ -4896,10 +4896,10 @@
         <v>20</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
@@ -4910,10 +4910,10 @@
         <v>20</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
@@ -4924,10 +4924,10 @@
         <v>20</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
@@ -4938,10 +4938,10 @@
         <v>20</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
@@ -4952,10 +4952,10 @@
         <v>20</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -4966,10 +4966,10 @@
         <v>20</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -4980,10 +4980,10 @@
         <v>20</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -4994,10 +4994,10 @@
         <v>20</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
@@ -5008,10 +5008,10 @@
         <v>20</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -5022,10 +5022,10 @@
         <v>20</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
@@ -5036,10 +5036,10 @@
         <v>20</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
@@ -5050,10 +5050,10 @@
         <v>20</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
@@ -5064,10 +5064,10 @@
         <v>20</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
@@ -5078,10 +5078,10 @@
         <v>20</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
@@ -5092,10 +5092,10 @@
         <v>20</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
@@ -5106,10 +5106,10 @@
         <v>20</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
@@ -5120,10 +5120,10 @@
         <v>20</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
@@ -5134,10 +5134,10 @@
         <v>20</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
@@ -5148,10 +5148,10 @@
         <v>20</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
@@ -5162,10 +5162,10 @@
         <v>20</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
@@ -5176,10 +5176,10 @@
         <v>20</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
@@ -5190,10 +5190,10 @@
         <v>20</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
@@ -5204,10 +5204,10 @@
         <v>22</v>
       </c>
       <c r="C285" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D285" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D285" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
@@ -5218,10 +5218,10 @@
         <v>22</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
@@ -5232,10 +5232,10 @@
         <v>22</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
@@ -5246,10 +5246,10 @@
         <v>22</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
@@ -5260,10 +5260,10 @@
         <v>22</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
@@ -5274,10 +5274,10 @@
         <v>22</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
@@ -5288,10 +5288,10 @@
         <v>22</v>
       </c>
       <c r="C291" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D291" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="D291" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
@@ -5302,10 +5302,10 @@
         <v>22</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
@@ -5316,10 +5316,10 @@
         <v>22</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
@@ -5330,10 +5330,10 @@
         <v>22</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
@@ -5344,10 +5344,10 @@
         <v>22</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
@@ -5358,10 +5358,10 @@
         <v>22</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
@@ -5372,10 +5372,10 @@
         <v>22</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
@@ -5386,10 +5386,10 @@
         <v>22</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
@@ -5400,10 +5400,10 @@
         <v>22</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
@@ -5414,10 +5414,10 @@
         <v>22</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
@@ -5428,10 +5428,10 @@
         <v>22</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
@@ -5442,10 +5442,10 @@
         <v>22</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
@@ -5456,10 +5456,10 @@
         <v>22</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
@@ -5470,10 +5470,10 @@
         <v>22</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
@@ -5484,10 +5484,10 @@
         <v>22</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
@@ -5498,10 +5498,10 @@
         <v>22</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
@@ -5512,10 +5512,10 @@
         <v>22</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
@@ -5526,10 +5526,10 @@
         <v>22</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
@@ -5540,10 +5540,10 @@
         <v>22</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
@@ -5554,10 +5554,10 @@
         <v>22</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
@@ -5568,10 +5568,10 @@
         <v>22</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
@@ -5582,10 +5582,10 @@
         <v>22</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
@@ -5596,10 +5596,10 @@
         <v>24</v>
       </c>
       <c r="C313" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D313" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D313" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
@@ -5610,10 +5610,10 @@
         <v>24</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
@@ -5624,10 +5624,10 @@
         <v>24</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
@@ -5638,10 +5638,10 @@
         <v>24</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
@@ -5652,10 +5652,10 @@
         <v>24</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
@@ -5666,10 +5666,10 @@
         <v>24</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
@@ -5680,10 +5680,10 @@
         <v>24</v>
       </c>
       <c r="C319" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D319" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="D319" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
@@ -5694,10 +5694,10 @@
         <v>24</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
@@ -5708,10 +5708,10 @@
         <v>24</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
@@ -5722,10 +5722,10 @@
         <v>24</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
@@ -5736,10 +5736,10 @@
         <v>24</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
@@ -5750,10 +5750,10 @@
         <v>24</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
@@ -5764,10 +5764,10 @@
         <v>24</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -5778,10 +5778,10 @@
         <v>24</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
@@ -5792,10 +5792,10 @@
         <v>24</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
@@ -5806,10 +5806,10 @@
         <v>24</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
@@ -5820,10 +5820,10 @@
         <v>24</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
@@ -5834,10 +5834,10 @@
         <v>24</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
@@ -5848,10 +5848,10 @@
         <v>24</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -5862,10 +5862,10 @@
         <v>24</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
@@ -5876,10 +5876,10 @@
         <v>26</v>
       </c>
       <c r="C333" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D333" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="D333" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
@@ -5890,10 +5890,10 @@
         <v>26</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
@@ -5904,10 +5904,10 @@
         <v>26</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
@@ -5918,10 +5918,10 @@
         <v>26</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
@@ -5932,10 +5932,10 @@
         <v>26</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
@@ -5946,10 +5946,10 @@
         <v>26</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
@@ -5960,10 +5960,10 @@
         <v>26</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
@@ -5974,10 +5974,10 @@
         <v>26</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
@@ -5988,10 +5988,10 @@
         <v>26</v>
       </c>
       <c r="C341" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D341" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="D341" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
@@ -6002,10 +6002,10 @@
         <v>26</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
@@ -6016,10 +6016,10 @@
         <v>26</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
@@ -6030,10 +6030,10 @@
         <v>26</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
@@ -6044,10 +6044,10 @@
         <v>26</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
@@ -6058,10 +6058,10 @@
         <v>26</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
@@ -6072,10 +6072,10 @@
         <v>26</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
@@ -6086,10 +6086,10 @@
         <v>26</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
@@ -6100,10 +6100,10 @@
         <v>26</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
@@ -6114,10 +6114,10 @@
         <v>26</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
@@ -6128,10 +6128,10 @@
         <v>26</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
@@ -6142,10 +6142,10 @@
         <v>26</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
@@ -6156,10 +6156,10 @@
         <v>26</v>
       </c>
       <c r="C353" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D353" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="D353" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
@@ -6170,10 +6170,10 @@
         <v>26</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
@@ -6184,10 +6184,10 @@
         <v>26</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
@@ -6198,10 +6198,10 @@
         <v>26</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
@@ -6212,10 +6212,10 @@
         <v>26</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
@@ -6226,10 +6226,10 @@
         <v>26</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
@@ -6240,10 +6240,10 @@
         <v>26</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
@@ -6254,10 +6254,10 @@
         <v>26</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
@@ -6268,10 +6268,10 @@
         <v>26</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
@@ -6282,10 +6282,10 @@
         <v>26</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
@@ -6296,10 +6296,10 @@
         <v>26</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
@@ -6310,10 +6310,10 @@
         <v>26</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
@@ -6324,10 +6324,10 @@
         <v>26</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
@@ -6338,10 +6338,10 @@
         <v>26</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
@@ -6352,10 +6352,10 @@
         <v>26</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
@@ -6366,10 +6366,10 @@
         <v>26</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
@@ -6380,10 +6380,10 @@
         <v>26</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
@@ -6394,10 +6394,10 @@
         <v>26</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
@@ -6408,10 +6408,10 @@
         <v>26</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
@@ -6422,10 +6422,10 @@
         <v>26</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
@@ -6436,10 +6436,10 @@
         <v>26</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
@@ -6450,10 +6450,10 @@
         <v>26</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
@@ -6464,10 +6464,10 @@
         <v>26</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
@@ -6478,10 +6478,10 @@
         <v>26</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
@@ -6492,10 +6492,10 @@
         <v>26</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/NHS consultancies mapping.xlsx.xlsx
+++ b/NHS consultancies mapping.xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NM2.WQGISDUV\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D611AA-530C-4ABB-9131-F1D0B33AC521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674A84F5-D4BC-4F20-9388-C558F3C9565C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7340E7F6-9FC5-4620-8510-CFC58B28CD68}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7340E7F6-9FC5-4620-8510-CFC58B28CD68}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="108">
   <si>
     <t>Consultancy</t>
   </si>
@@ -361,13 +361,16 @@
   </si>
   <si>
     <t>Analytical product development (e.g. dashboards)</t>
+  </si>
+  <si>
+    <t>https://www.mse.nhs.uk/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,6 +395,15 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -426,10 +438,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -438,8 +451,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
@@ -1084,7 +1099,9 @@
       <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="6" t="s">
+        <v>107</v>
+      </c>
       <c r="D6" s="5" t="s">
         <v>89</v>
       </c>
@@ -1202,9 +1219,12 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C6" r:id="rId1" xr:uid="{33058541-B9B4-4B90-AEF8-D256F81AAA01}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/NHS consultancies mapping.xlsx.xlsx
+++ b/NHS consultancies mapping.xlsx.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NM2.WQGISDUV\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674A84F5-D4BC-4F20-9388-C558F3C9565C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98BE26E1-7738-4ADA-A1D9-9E7A1449B1A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7340E7F6-9FC5-4620-8510-CFC58B28CD68}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7340E7F6-9FC5-4620-8510-CFC58B28CD68}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="1" r:id="rId1"/>
     <sheet name="Capability" sheetId="2" r:id="rId2"/>
+    <sheet name="ChangeLog" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="120">
   <si>
     <t>Consultancy</t>
   </si>
@@ -141,9 +142,6 @@
     <t>Strategic commissioning</t>
   </si>
   <si>
-    <t>Evaluation (qualitative)</t>
-  </si>
-  <si>
     <t>Workforce strategy</t>
   </si>
   <si>
@@ -364,6 +362,45 @@
   </si>
   <si>
     <t>https://www.mse.nhs.uk/</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Requested by</t>
+  </si>
+  <si>
+    <t>Details of change</t>
+  </si>
+  <si>
+    <t>Paul Mason</t>
+  </si>
+  <si>
+    <t>Strategy Unit</t>
+  </si>
+  <si>
+    <t>Renamed 'Evaluation (qualitative)' to 'Qualitative evaluation' and moved from Strategy &amp; advisory to Analytics &amp; evaluation (affects 7 consultancies). Added 'Quantitative evaluation (including quasi-experimental methods)', 'Mixed-method evaluation', and 'Large-scale complex transformation programme evaluation' to Analytics &amp; evaluation for The Strategy Unit.</t>
+  </si>
+  <si>
+    <t>Sue Hunter</t>
+  </si>
+  <si>
+    <t>TPHC</t>
+  </si>
+  <si>
+    <t>First version of mapping</t>
+  </si>
+  <si>
+    <t>Quantitative evaluation (including quasi-experimental methods)</t>
+  </si>
+  <si>
+    <t>Mixed-methods evaluation</t>
+  </si>
+  <si>
+    <t>Large-scale complex transformation programme evaluation</t>
+  </si>
+  <si>
+    <t>Qualitative evaluation</t>
   </si>
 </sst>
 </file>
@@ -442,7 +479,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -452,12 +489,130 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="13">
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -562,101 +717,6 @@
         <scheme val="none"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -671,26 +731,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C9572655-E052-4EE2-BFDB-5C5E9A5C4E7C}" name="Table2" displayName="Table2" ref="A1:D14" totalsRowShown="0" headerRowDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C9572655-E052-4EE2-BFDB-5C5E9A5C4E7C}" name="Table2" displayName="Table2" ref="A1:D14" totalsRowShown="0" headerRowDxfId="12">
   <autoFilter ref="A1:D14" xr:uid="{C9572655-E052-4EE2-BFDB-5C5E9A5C4E7C}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{89565BE1-9E7B-44AD-9BE1-0955CF351119}" name="Consultancy_ID"/>
-    <tableColumn id="2" xr3:uid="{3E1BAA85-9A9A-44AB-8942-61C854CAE23C}" name="Consultancy" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{F38AAC86-9FBB-4D44-97D2-B2726AF15405}" name="Website" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{512955EA-1088-4328-982A-A9EC35512082}" name="Geography covered" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{3E1BAA85-9A9A-44AB-8942-61C854CAE23C}" name="Consultancy" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{F38AAC86-9FBB-4D44-97D2-B2726AF15405}" name="Website" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{512955EA-1088-4328-982A-A9EC35512082}" name="Geography covered" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C15222F8-4F91-4902-93B6-E3D2567E6BB4}" name="Table1" displayName="Table1" ref="A1:D377" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:D377" xr:uid="{C15222F8-4F91-4902-93B6-E3D2567E6BB4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C15222F8-4F91-4902-93B6-E3D2567E6BB4}" name="Table1" displayName="Table1" ref="A1:D380" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:D380" xr:uid="{C15222F8-4F91-4902-93B6-E3D2567E6BB4}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Evaluation (qualitative)"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{943C8565-D5B5-42D2-BC2C-032AFD7866B7}" name="Consultancy_ID"/>
     <tableColumn id="2" xr3:uid="{788DA50E-E6D8-47BC-96E2-373425F6A9C2}" name="Consultancy" dataDxfId="6"/>
     <tableColumn id="3" xr3:uid="{81EB959A-1CF9-4AA5-B932-0FD91DD22EB5}" name="Service Theme" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{75BF1020-0A01-43AE-9EE7-AF049FC1AF2D}" name="Capability" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{1B94633E-FA1C-4C8F-ACCF-3CEA2D177197}" name="Table3" displayName="Table3" ref="A1:D3" totalsRowShown="0">
+  <autoFilter ref="A1:D3" xr:uid="{1B94633E-FA1C-4C8F-ACCF-3CEA2D177197}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{ED882561-2A3A-4467-8041-B47B8678BF5F}" name="Date" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{48E13BE6-D724-4B51-82A5-CC545C4A2AB4}" name="Requested by" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{74ADF0EA-A6AF-4B11-A715-2DB85245318A}" name="Consultancy" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{186B7640-AABE-4921-8D4C-5E30531A7720}" name="Details of change" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1024,7 +1103,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1047,7 +1126,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1061,7 +1140,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1075,7 +1154,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1089,7 +1168,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1100,10 +1179,10 @@
         <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1117,7 +1196,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1131,7 +1210,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1145,7 +1224,7 @@
         <v>17</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1159,7 +1238,7 @@
         <v>19</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1173,7 +1252,7 @@
         <v>21</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1187,7 +1266,7 @@
         <v>23</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1201,7 +1280,7 @@
         <v>25</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1215,7 +1294,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1231,7 +1310,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07FEE677-ED03-44CB-AFA9-A574AE666959}">
-  <dimension ref="A1:D377"/>
+  <dimension ref="A1:D380"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1242,7 +1321,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1254,7 +1333,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1262,13 +1341,13 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1276,13 +1355,13 @@
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1290,7 +1369,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>32</v>
@@ -1304,13 +1383,13 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1318,13 +1397,13 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1332,13 +1411,13 @@
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1346,13 +1425,13 @@
         <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1360,13 +1439,13 @@
         <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1374,13 +1453,13 @@
         <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1</v>
       </c>
@@ -1388,13 +1467,13 @@
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1</v>
       </c>
@@ -1402,13 +1481,13 @@
         <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1</v>
       </c>
@@ -1416,13 +1495,13 @@
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1</v>
       </c>
@@ -1430,13 +1509,13 @@
         <v>3</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1</v>
       </c>
@@ -1444,13 +1523,13 @@
         <v>3</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1</v>
       </c>
@@ -1458,13 +1537,13 @@
         <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1</v>
       </c>
@@ -1472,13 +1551,13 @@
         <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1</v>
       </c>
@@ -1486,13 +1565,13 @@
         <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1</v>
       </c>
@@ -1500,13 +1579,13 @@
         <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1</v>
       </c>
@@ -1514,13 +1593,13 @@
         <v>3</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>1</v>
       </c>
@@ -1528,13 +1607,13 @@
         <v>3</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1</v>
       </c>
@@ -1542,13 +1621,13 @@
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1</v>
       </c>
@@ -1556,13 +1635,13 @@
         <v>3</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1</v>
       </c>
@@ -1570,13 +1649,13 @@
         <v>3</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>1</v>
       </c>
@@ -1584,13 +1663,13 @@
         <v>3</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1</v>
       </c>
@@ -1598,13 +1677,13 @@
         <v>3</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1</v>
       </c>
@@ -1612,13 +1691,13 @@
         <v>3</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>1</v>
       </c>
@@ -1626,13 +1705,13 @@
         <v>3</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>1</v>
       </c>
@@ -1640,13 +1719,13 @@
         <v>3</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>1</v>
       </c>
@@ -1654,13 +1733,13 @@
         <v>3</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>1</v>
       </c>
@@ -1668,13 +1747,13 @@
         <v>3</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>1</v>
       </c>
@@ -1682,13 +1761,13 @@
         <v>3</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>1</v>
       </c>
@@ -1696,13 +1775,13 @@
         <v>3</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>1</v>
       </c>
@@ -1710,13 +1789,13 @@
         <v>3</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>1</v>
       </c>
@@ -1724,13 +1803,13 @@
         <v>3</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>1</v>
       </c>
@@ -1738,13 +1817,13 @@
         <v>3</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>1</v>
       </c>
@@ -1752,13 +1831,13 @@
         <v>3</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1</v>
       </c>
@@ -1766,13 +1845,13 @@
         <v>3</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>1</v>
       </c>
@@ -1780,13 +1859,13 @@
         <v>3</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1</v>
       </c>
@@ -1794,13 +1873,13 @@
         <v>3</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2</v>
       </c>
@@ -1808,13 +1887,13 @@
         <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2</v>
       </c>
@@ -1822,13 +1901,13 @@
         <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>3</v>
       </c>
@@ -1836,13 +1915,13 @@
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>3</v>
       </c>
@@ -1850,13 +1929,13 @@
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>3</v>
       </c>
@@ -1864,13 +1943,13 @@
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>3</v>
       </c>
@@ -1878,13 +1957,13 @@
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>3</v>
       </c>
@@ -1892,13 +1971,13 @@
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>3</v>
       </c>
@@ -1906,13 +1985,13 @@
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>3</v>
       </c>
@@ -1920,13 +1999,13 @@
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>3</v>
       </c>
@@ -1934,13 +2013,13 @@
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>3</v>
       </c>
@@ -1948,13 +2027,13 @@
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>3</v>
       </c>
@@ -1962,13 +2041,13 @@
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>3</v>
       </c>
@@ -1976,13 +2055,13 @@
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>3</v>
       </c>
@@ -1990,13 +2069,13 @@
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>3</v>
       </c>
@@ -2004,13 +2083,13 @@
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>3</v>
       </c>
@@ -2018,13 +2097,13 @@
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>4</v>
       </c>
@@ -2032,13 +2111,13 @@
         <v>9</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>4</v>
       </c>
@@ -2046,13 +2125,13 @@
         <v>9</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>4</v>
       </c>
@@ -2060,13 +2139,13 @@
         <v>9</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>4</v>
       </c>
@@ -2074,7 +2153,7 @@
         <v>9</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>32</v>
@@ -2088,13 +2167,13 @@
         <v>9</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>4</v>
       </c>
@@ -2102,13 +2181,13 @@
         <v>9</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>4</v>
       </c>
@@ -2116,13 +2195,13 @@
         <v>9</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>4</v>
       </c>
@@ -2130,13 +2209,13 @@
         <v>9</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>4</v>
       </c>
@@ -2144,13 +2223,13 @@
         <v>9</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>4</v>
       </c>
@@ -2158,13 +2237,13 @@
         <v>9</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>4</v>
       </c>
@@ -2172,13 +2251,13 @@
         <v>9</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>4</v>
       </c>
@@ -2186,13 +2265,13 @@
         <v>9</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>4</v>
       </c>
@@ -2200,13 +2279,13 @@
         <v>9</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>4</v>
       </c>
@@ -2214,13 +2293,13 @@
         <v>9</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>4</v>
       </c>
@@ -2228,13 +2307,13 @@
         <v>9</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>4</v>
       </c>
@@ -2242,13 +2321,13 @@
         <v>9</v>
       </c>
       <c r="C72" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>4</v>
       </c>
@@ -2256,13 +2335,13 @@
         <v>9</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>4</v>
       </c>
@@ -2270,13 +2349,13 @@
         <v>9</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>4</v>
       </c>
@@ -2284,13 +2363,13 @@
         <v>9</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>4</v>
       </c>
@@ -2298,13 +2377,13 @@
         <v>9</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>4</v>
       </c>
@@ -2312,13 +2391,13 @@
         <v>9</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>4</v>
       </c>
@@ -2326,13 +2405,13 @@
         <v>9</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>4</v>
       </c>
@@ -2340,13 +2419,13 @@
         <v>9</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>4</v>
       </c>
@@ -2354,13 +2433,13 @@
         <v>9</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>4</v>
       </c>
@@ -2368,13 +2447,13 @@
         <v>9</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>4</v>
       </c>
@@ -2382,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>4</v>
       </c>
@@ -2396,13 +2475,13 @@
         <v>9</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>4</v>
       </c>
@@ -2410,13 +2489,13 @@
         <v>9</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>4</v>
       </c>
@@ -2424,13 +2503,13 @@
         <v>9</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>4</v>
       </c>
@@ -2438,13 +2517,13 @@
         <v>9</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>4</v>
       </c>
@@ -2452,13 +2531,13 @@
         <v>9</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>4</v>
       </c>
@@ -2466,13 +2545,13 @@
         <v>9</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>4</v>
       </c>
@@ -2480,13 +2559,13 @@
         <v>9</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>4</v>
       </c>
@@ -2494,13 +2573,13 @@
         <v>9</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>4</v>
       </c>
@@ -2508,13 +2587,13 @@
         <v>9</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>4</v>
       </c>
@@ -2522,13 +2601,13 @@
         <v>9</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>4</v>
       </c>
@@ -2536,13 +2615,13 @@
         <v>9</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>4</v>
       </c>
@@ -2550,13 +2629,13 @@
         <v>9</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>4</v>
       </c>
@@ -2564,13 +2643,13 @@
         <v>9</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>4</v>
       </c>
@@ -2578,13 +2657,13 @@
         <v>9</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>4</v>
       </c>
@@ -2592,13 +2671,13 @@
         <v>9</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>4</v>
       </c>
@@ -2606,13 +2685,13 @@
         <v>9</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>4</v>
       </c>
@@ -2620,13 +2699,13 @@
         <v>9</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>4</v>
       </c>
@@ -2634,13 +2713,13 @@
         <v>9</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>4</v>
       </c>
@@ -2648,13 +2727,13 @@
         <v>9</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>4</v>
       </c>
@@ -2662,13 +2741,13 @@
         <v>9</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>4</v>
       </c>
@@ -2676,13 +2755,13 @@
         <v>9</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>4</v>
       </c>
@@ -2690,13 +2769,13 @@
         <v>9</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>4</v>
       </c>
@@ -2704,13 +2783,13 @@
         <v>9</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>4</v>
       </c>
@@ -2718,13 +2797,13 @@
         <v>9</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>4</v>
       </c>
@@ -2732,13 +2811,13 @@
         <v>9</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>4</v>
       </c>
@@ -2746,13 +2825,13 @@
         <v>9</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>4</v>
       </c>
@@ -2760,13 +2839,13 @@
         <v>9</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>4</v>
       </c>
@@ -2774,13 +2853,13 @@
         <v>9</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>5</v>
       </c>
@@ -2788,13 +2867,13 @@
         <v>11</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>5</v>
       </c>
@@ -2802,13 +2881,13 @@
         <v>11</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>5</v>
       </c>
@@ -2816,13 +2895,13 @@
         <v>11</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>5</v>
       </c>
@@ -2830,10 +2909,10 @@
         <v>11</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -2844,13 +2923,13 @@
         <v>11</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>5</v>
       </c>
@@ -2858,13 +2937,13 @@
         <v>11</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>5</v>
       </c>
@@ -2872,13 +2951,13 @@
         <v>11</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>5</v>
       </c>
@@ -2886,13 +2965,13 @@
         <v>11</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>5</v>
       </c>
@@ -2900,13 +2979,13 @@
         <v>11</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>5</v>
       </c>
@@ -2914,13 +2993,13 @@
         <v>11</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>5</v>
       </c>
@@ -2928,13 +3007,13 @@
         <v>11</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>5</v>
       </c>
@@ -2942,13 +3021,13 @@
         <v>11</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>5</v>
       </c>
@@ -2956,13 +3035,13 @@
         <v>11</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>5</v>
       </c>
@@ -2970,13 +3049,13 @@
         <v>11</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>5</v>
       </c>
@@ -2984,13 +3063,13 @@
         <v>11</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>5</v>
       </c>
@@ -2998,13 +3077,13 @@
         <v>11</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>5</v>
       </c>
@@ -3012,13 +3091,13 @@
         <v>11</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>5</v>
       </c>
@@ -3026,13 +3105,13 @@
         <v>11</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>5</v>
       </c>
@@ -3040,13 +3119,13 @@
         <v>11</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>5</v>
       </c>
@@ -3054,13 +3133,13 @@
         <v>11</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>5</v>
       </c>
@@ -3068,13 +3147,13 @@
         <v>11</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>5</v>
       </c>
@@ -3082,13 +3161,13 @@
         <v>11</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>5</v>
       </c>
@@ -3096,13 +3175,13 @@
         <v>11</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>5</v>
       </c>
@@ -3110,13 +3189,13 @@
         <v>11</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>6</v>
       </c>
@@ -3124,13 +3203,13 @@
         <v>12</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>6</v>
       </c>
@@ -3138,13 +3217,13 @@
         <v>12</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>6</v>
       </c>
@@ -3152,13 +3231,13 @@
         <v>12</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>6</v>
       </c>
@@ -3166,13 +3245,13 @@
         <v>12</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>6</v>
       </c>
@@ -3180,13 +3259,13 @@
         <v>12</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>6</v>
       </c>
@@ -3194,13 +3273,13 @@
         <v>12</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>6</v>
       </c>
@@ -3208,13 +3287,13 @@
         <v>12</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>6</v>
       </c>
@@ -3222,13 +3301,13 @@
         <v>12</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>6</v>
       </c>
@@ -3236,13 +3315,13 @@
         <v>12</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>6</v>
       </c>
@@ -3250,13 +3329,13 @@
         <v>12</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>6</v>
       </c>
@@ -3264,13 +3343,13 @@
         <v>12</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>6</v>
       </c>
@@ -3278,13 +3357,13 @@
         <v>12</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>6</v>
       </c>
@@ -3292,13 +3371,13 @@
         <v>12</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>6</v>
       </c>
@@ -3306,13 +3385,13 @@
         <v>12</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>7</v>
       </c>
@@ -3320,13 +3399,13 @@
         <v>14</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>7</v>
       </c>
@@ -3334,13 +3413,13 @@
         <v>14</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>7</v>
       </c>
@@ -3348,13 +3427,13 @@
         <v>14</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>7</v>
       </c>
@@ -3362,13 +3441,13 @@
         <v>14</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>7</v>
       </c>
@@ -3376,13 +3455,13 @@
         <v>14</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>7</v>
       </c>
@@ -3390,13 +3469,13 @@
         <v>14</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>7</v>
       </c>
@@ -3404,13 +3483,13 @@
         <v>14</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>7</v>
       </c>
@@ -3418,13 +3497,13 @@
         <v>14</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>7</v>
       </c>
@@ -3432,13 +3511,13 @@
         <v>14</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>7</v>
       </c>
@@ -3446,13 +3525,13 @@
         <v>14</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>7</v>
       </c>
@@ -3460,13 +3539,13 @@
         <v>14</v>
       </c>
       <c r="C159" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D159" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D159" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>7</v>
       </c>
@@ -3474,13 +3553,13 @@
         <v>14</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>7</v>
       </c>
@@ -3488,13 +3567,13 @@
         <v>14</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>7</v>
       </c>
@@ -3502,13 +3581,13 @@
         <v>14</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>7</v>
       </c>
@@ -3516,13 +3595,13 @@
         <v>14</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>7</v>
       </c>
@@ -3530,13 +3609,13 @@
         <v>14</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>7</v>
       </c>
@@ -3544,13 +3623,13 @@
         <v>14</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>7</v>
       </c>
@@ -3558,13 +3637,13 @@
         <v>14</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>7</v>
       </c>
@@ -3572,13 +3651,13 @@
         <v>14</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>7</v>
       </c>
@@ -3586,13 +3665,13 @@
         <v>14</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>7</v>
       </c>
@@ -3600,13 +3679,13 @@
         <v>14</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>7</v>
       </c>
@@ -3614,13 +3693,13 @@
         <v>14</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>7</v>
       </c>
@@ -3628,13 +3707,13 @@
         <v>14</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>7</v>
       </c>
@@ -3642,13 +3721,13 @@
         <v>14</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>8</v>
       </c>
@@ -3656,13 +3735,13 @@
         <v>16</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>8</v>
       </c>
@@ -3670,13 +3749,13 @@
         <v>16</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>8</v>
       </c>
@@ -3684,13 +3763,13 @@
         <v>16</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>8</v>
       </c>
@@ -3698,13 +3777,13 @@
         <v>16</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>8</v>
       </c>
@@ -3712,10 +3791,10 @@
         <v>16</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
@@ -3726,13 +3805,13 @@
         <v>16</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>8</v>
       </c>
@@ -3740,13 +3819,13 @@
         <v>16</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>8</v>
       </c>
@@ -3754,13 +3833,13 @@
         <v>16</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>8</v>
       </c>
@@ -3768,13 +3847,13 @@
         <v>16</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>8</v>
       </c>
@@ -3782,13 +3861,13 @@
         <v>16</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>8</v>
       </c>
@@ -3796,13 +3875,13 @@
         <v>16</v>
       </c>
       <c r="C183" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D183" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D183" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>8</v>
       </c>
@@ -3810,13 +3889,13 @@
         <v>16</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>8</v>
       </c>
@@ -3824,13 +3903,13 @@
         <v>16</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>8</v>
       </c>
@@ -3838,13 +3917,13 @@
         <v>16</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>8</v>
       </c>
@@ -3852,13 +3931,13 @@
         <v>16</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>8</v>
       </c>
@@ -3866,13 +3945,13 @@
         <v>16</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>8</v>
       </c>
@@ -3880,13 +3959,13 @@
         <v>16</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>8</v>
       </c>
@@ -3894,13 +3973,13 @@
         <v>16</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>8</v>
       </c>
@@ -3908,13 +3987,13 @@
         <v>16</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>8</v>
       </c>
@@ -3922,13 +4001,13 @@
         <v>16</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>8</v>
       </c>
@@ -3936,13 +4015,13 @@
         <v>16</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>8</v>
       </c>
@@ -3950,13 +4029,13 @@
         <v>16</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>8</v>
       </c>
@@ -3964,13 +4043,13 @@
         <v>16</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>9</v>
       </c>
@@ -3978,13 +4057,13 @@
         <v>18</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>9</v>
       </c>
@@ -3992,13 +4071,13 @@
         <v>18</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>9</v>
       </c>
@@ -4006,13 +4085,13 @@
         <v>18</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>9</v>
       </c>
@@ -4020,13 +4099,13 @@
         <v>18</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>9</v>
       </c>
@@ -4034,13 +4113,13 @@
         <v>18</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>9</v>
       </c>
@@ -4048,13 +4127,13 @@
         <v>18</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>9</v>
       </c>
@@ -4062,13 +4141,13 @@
         <v>18</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>9</v>
       </c>
@@ -4076,13 +4155,13 @@
         <v>18</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>9</v>
       </c>
@@ -4090,13 +4169,13 @@
         <v>18</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>9</v>
       </c>
@@ -4104,13 +4183,13 @@
         <v>18</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>9</v>
       </c>
@@ -4118,13 +4197,13 @@
         <v>18</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>9</v>
       </c>
@@ -4132,13 +4211,13 @@
         <v>18</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>9</v>
       </c>
@@ -4146,13 +4225,13 @@
         <v>18</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>9</v>
       </c>
@@ -4160,13 +4239,13 @@
         <v>18</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>9</v>
       </c>
@@ -4174,13 +4253,13 @@
         <v>18</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>9</v>
       </c>
@@ -4188,13 +4267,13 @@
         <v>18</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>9</v>
       </c>
@@ -4202,13 +4281,13 @@
         <v>18</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>9</v>
       </c>
@@ -4216,13 +4295,13 @@
         <v>18</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>9</v>
       </c>
@@ -4230,13 +4309,13 @@
         <v>18</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>9</v>
       </c>
@@ -4244,13 +4323,13 @@
         <v>18</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>9</v>
       </c>
@@ -4258,13 +4337,13 @@
         <v>18</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>9</v>
       </c>
@@ -4272,13 +4351,13 @@
         <v>18</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>9</v>
       </c>
@@ -4286,13 +4365,13 @@
         <v>18</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>9</v>
       </c>
@@ -4300,13 +4379,13 @@
         <v>18</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>9</v>
       </c>
@@ -4314,13 +4393,13 @@
         <v>18</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>9</v>
       </c>
@@ -4328,13 +4407,13 @@
         <v>18</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>9</v>
       </c>
@@ -4342,13 +4421,13 @@
         <v>18</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>9</v>
       </c>
@@ -4356,13 +4435,13 @@
         <v>18</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>9</v>
       </c>
@@ -4370,13 +4449,13 @@
         <v>18</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>9</v>
       </c>
@@ -4384,13 +4463,13 @@
         <v>18</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>9</v>
       </c>
@@ -4398,13 +4477,13 @@
         <v>18</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>9</v>
       </c>
@@ -4412,13 +4491,13 @@
         <v>18</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>9</v>
       </c>
@@ -4426,13 +4505,13 @@
         <v>18</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>9</v>
       </c>
@@ -4440,13 +4519,13 @@
         <v>18</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>9</v>
       </c>
@@ -4454,13 +4533,13 @@
         <v>18</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>9</v>
       </c>
@@ -4468,13 +4547,13 @@
         <v>18</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>9</v>
       </c>
@@ -4482,13 +4561,13 @@
         <v>18</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>9</v>
       </c>
@@ -4496,13 +4575,13 @@
         <v>18</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>9</v>
       </c>
@@ -4510,13 +4589,13 @@
         <v>18</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>9</v>
       </c>
@@ -4524,13 +4603,13 @@
         <v>18</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>9</v>
       </c>
@@ -4538,13 +4617,13 @@
         <v>18</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>9</v>
       </c>
@@ -4552,13 +4631,13 @@
         <v>18</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>9</v>
       </c>
@@ -4566,13 +4645,13 @@
         <v>18</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>10</v>
       </c>
@@ -4580,13 +4659,13 @@
         <v>20</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>10</v>
       </c>
@@ -4594,13 +4673,13 @@
         <v>20</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>10</v>
       </c>
@@ -4608,13 +4687,13 @@
         <v>20</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>10</v>
       </c>
@@ -4622,13 +4701,13 @@
         <v>20</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>10</v>
       </c>
@@ -4636,10 +4715,10 @@
         <v>20</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -4650,13 +4729,13 @@
         <v>20</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>10</v>
       </c>
@@ -4664,13 +4743,13 @@
         <v>20</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>10</v>
       </c>
@@ -4678,13 +4757,13 @@
         <v>20</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>10</v>
       </c>
@@ -4692,13 +4771,13 @@
         <v>20</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>10</v>
       </c>
@@ -4706,13 +4785,13 @@
         <v>20</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>10</v>
       </c>
@@ -4720,13 +4799,13 @@
         <v>20</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>10</v>
       </c>
@@ -4734,13 +4813,13 @@
         <v>20</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>10</v>
       </c>
@@ -4748,13 +4827,13 @@
         <v>20</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>10</v>
       </c>
@@ -4762,13 +4841,13 @@
         <v>20</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>10</v>
       </c>
@@ -4776,13 +4855,13 @@
         <v>20</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>10</v>
       </c>
@@ -4790,13 +4869,13 @@
         <v>20</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>10</v>
       </c>
@@ -4804,13 +4883,13 @@
         <v>20</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>10</v>
       </c>
@@ -4818,13 +4897,13 @@
         <v>20</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>10</v>
       </c>
@@ -4832,13 +4911,13 @@
         <v>20</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>10</v>
       </c>
@@ -4846,13 +4925,13 @@
         <v>20</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>10</v>
       </c>
@@ -4860,13 +4939,13 @@
         <v>20</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>10</v>
       </c>
@@ -4874,13 +4953,13 @@
         <v>20</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>10</v>
       </c>
@@ -4888,13 +4967,13 @@
         <v>20</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>10</v>
       </c>
@@ -4902,13 +4981,13 @@
         <v>20</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>10</v>
       </c>
@@ -4916,13 +4995,13 @@
         <v>20</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>10</v>
       </c>
@@ -4930,13 +5009,13 @@
         <v>20</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>10</v>
       </c>
@@ -4944,13 +5023,13 @@
         <v>20</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>10</v>
       </c>
@@ -4958,13 +5037,13 @@
         <v>20</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>10</v>
       </c>
@@ -4972,13 +5051,13 @@
         <v>20</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>10</v>
       </c>
@@ -4986,13 +5065,13 @@
         <v>20</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>10</v>
       </c>
@@ -5000,13 +5079,13 @@
         <v>20</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>10</v>
       </c>
@@ -5014,13 +5093,13 @@
         <v>20</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>10</v>
       </c>
@@ -5028,13 +5107,13 @@
         <v>20</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>10</v>
       </c>
@@ -5042,13 +5121,13 @@
         <v>20</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>10</v>
       </c>
@@ -5056,13 +5135,13 @@
         <v>20</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>10</v>
       </c>
@@ -5070,13 +5149,13 @@
         <v>20</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>10</v>
       </c>
@@ -5084,13 +5163,13 @@
         <v>20</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>10</v>
       </c>
@@ -5098,13 +5177,13 @@
         <v>20</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>10</v>
       </c>
@@ -5112,13 +5191,13 @@
         <v>20</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>10</v>
       </c>
@@ -5126,13 +5205,13 @@
         <v>20</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>10</v>
       </c>
@@ -5140,13 +5219,13 @@
         <v>20</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>10</v>
       </c>
@@ -5154,13 +5233,13 @@
         <v>20</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>10</v>
       </c>
@@ -5168,13 +5247,13 @@
         <v>20</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>10</v>
       </c>
@@ -5182,13 +5261,13 @@
         <v>20</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>10</v>
       </c>
@@ -5196,13 +5275,13 @@
         <v>20</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>10</v>
       </c>
@@ -5210,13 +5289,13 @@
         <v>20</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>11</v>
       </c>
@@ -5224,13 +5303,13 @@
         <v>22</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>11</v>
       </c>
@@ -5238,13 +5317,13 @@
         <v>22</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>11</v>
       </c>
@@ -5252,13 +5331,13 @@
         <v>22</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>11</v>
       </c>
@@ -5266,13 +5345,13 @@
         <v>22</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>11</v>
       </c>
@@ -5280,13 +5359,13 @@
         <v>22</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>11</v>
       </c>
@@ -5294,13 +5373,13 @@
         <v>22</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>11</v>
       </c>
@@ -5308,13 +5387,13 @@
         <v>22</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>11</v>
       </c>
@@ -5322,13 +5401,13 @@
         <v>22</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>11</v>
       </c>
@@ -5336,13 +5415,13 @@
         <v>22</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>11</v>
       </c>
@@ -5350,13 +5429,13 @@
         <v>22</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>11</v>
       </c>
@@ -5364,13 +5443,13 @@
         <v>22</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>11</v>
       </c>
@@ -5378,13 +5457,13 @@
         <v>22</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>11</v>
       </c>
@@ -5392,13 +5471,13 @@
         <v>22</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>11</v>
       </c>
@@ -5406,13 +5485,13 @@
         <v>22</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>11</v>
       </c>
@@ -5420,13 +5499,13 @@
         <v>22</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>11</v>
       </c>
@@ -5434,13 +5513,13 @@
         <v>22</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>11</v>
       </c>
@@ -5448,13 +5527,13 @@
         <v>22</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>11</v>
       </c>
@@ -5462,13 +5541,13 @@
         <v>22</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>11</v>
       </c>
@@ -5476,13 +5555,13 @@
         <v>22</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>11</v>
       </c>
@@ -5490,13 +5569,13 @@
         <v>22</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>11</v>
       </c>
@@ -5504,13 +5583,13 @@
         <v>22</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>11</v>
       </c>
@@ -5518,13 +5597,13 @@
         <v>22</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>11</v>
       </c>
@@ -5532,13 +5611,13 @@
         <v>22</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>11</v>
       </c>
@@ -5546,13 +5625,13 @@
         <v>22</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>11</v>
       </c>
@@ -5560,13 +5639,13 @@
         <v>22</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>11</v>
       </c>
@@ -5574,13 +5653,13 @@
         <v>22</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>11</v>
       </c>
@@ -5588,13 +5667,13 @@
         <v>22</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>11</v>
       </c>
@@ -5602,13 +5681,13 @@
         <v>22</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>12</v>
       </c>
@@ -5616,13 +5695,13 @@
         <v>24</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>12</v>
       </c>
@@ -5630,13 +5709,13 @@
         <v>24</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>12</v>
       </c>
@@ -5644,13 +5723,13 @@
         <v>24</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>12</v>
       </c>
@@ -5658,10 +5737,10 @@
         <v>24</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
@@ -5672,13 +5751,13 @@
         <v>24</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>12</v>
       </c>
@@ -5686,13 +5765,13 @@
         <v>24</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>12</v>
       </c>
@@ -5700,13 +5779,13 @@
         <v>24</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>12</v>
       </c>
@@ -5714,13 +5793,13 @@
         <v>24</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>12</v>
       </c>
@@ -5728,13 +5807,13 @@
         <v>24</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>12</v>
       </c>
@@ -5742,13 +5821,13 @@
         <v>24</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>12</v>
       </c>
@@ -5756,13 +5835,13 @@
         <v>24</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>12</v>
       </c>
@@ -5770,13 +5849,13 @@
         <v>24</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>12</v>
       </c>
@@ -5784,13 +5863,13 @@
         <v>24</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>12</v>
       </c>
@@ -5798,13 +5877,13 @@
         <v>24</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>12</v>
       </c>
@@ -5812,13 +5891,13 @@
         <v>24</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>12</v>
       </c>
@@ -5826,13 +5905,13 @@
         <v>24</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>12</v>
       </c>
@@ -5840,13 +5919,13 @@
         <v>24</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>12</v>
       </c>
@@ -5854,13 +5933,13 @@
         <v>24</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>12</v>
       </c>
@@ -5868,13 +5947,13 @@
         <v>24</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>12</v>
       </c>
@@ -5882,13 +5961,13 @@
         <v>24</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>13</v>
       </c>
@@ -5896,13 +5975,13 @@
         <v>26</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>13</v>
       </c>
@@ -5910,13 +5989,13 @@
         <v>26</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D334" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>13</v>
       </c>
@@ -5924,13 +6003,13 @@
         <v>26</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>13</v>
       </c>
@@ -5938,10 +6017,10 @@
         <v>26</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
@@ -5952,13 +6031,13 @@
         <v>26</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>13</v>
       </c>
@@ -5966,13 +6045,13 @@
         <v>26</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>13</v>
       </c>
@@ -5980,13 +6059,13 @@
         <v>26</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>13</v>
       </c>
@@ -5994,13 +6073,13 @@
         <v>26</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>13</v>
       </c>
@@ -6008,13 +6087,13 @@
         <v>26</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>13</v>
       </c>
@@ -6022,13 +6101,13 @@
         <v>26</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>13</v>
       </c>
@@ -6036,13 +6115,13 @@
         <v>26</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>13</v>
       </c>
@@ -6050,13 +6129,13 @@
         <v>26</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>13</v>
       </c>
@@ -6064,13 +6143,13 @@
         <v>26</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>13</v>
       </c>
@@ -6078,13 +6157,13 @@
         <v>26</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>13</v>
       </c>
@@ -6092,13 +6171,13 @@
         <v>26</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>13</v>
       </c>
@@ -6106,13 +6185,13 @@
         <v>26</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>13</v>
       </c>
@@ -6120,13 +6199,13 @@
         <v>26</v>
       </c>
       <c r="C349" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D349" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D349" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="350" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>13</v>
       </c>
@@ -6134,13 +6213,13 @@
         <v>26</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>13</v>
       </c>
@@ -6148,13 +6227,13 @@
         <v>26</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>13</v>
       </c>
@@ -6162,13 +6241,13 @@
         <v>26</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>13</v>
       </c>
@@ -6176,13 +6255,13 @@
         <v>26</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>13</v>
       </c>
@@ -6190,13 +6269,13 @@
         <v>26</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>13</v>
       </c>
@@ -6204,13 +6283,13 @@
         <v>26</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>13</v>
       </c>
@@ -6218,13 +6297,13 @@
         <v>26</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>13</v>
       </c>
@@ -6232,13 +6311,13 @@
         <v>26</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>13</v>
       </c>
@@ -6246,13 +6325,13 @@
         <v>26</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>13</v>
       </c>
@@ -6260,13 +6339,13 @@
         <v>26</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>13</v>
       </c>
@@ -6274,13 +6353,13 @@
         <v>26</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>13</v>
       </c>
@@ -6288,13 +6367,13 @@
         <v>26</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>13</v>
       </c>
@@ -6302,13 +6381,13 @@
         <v>26</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>13</v>
       </c>
@@ -6316,13 +6395,13 @@
         <v>26</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>13</v>
       </c>
@@ -6330,13 +6409,13 @@
         <v>26</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>13</v>
       </c>
@@ -6344,13 +6423,13 @@
         <v>26</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>13</v>
       </c>
@@ -6358,13 +6437,13 @@
         <v>26</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>13</v>
       </c>
@@ -6372,13 +6451,13 @@
         <v>26</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>13</v>
       </c>
@@ -6386,13 +6465,13 @@
         <v>26</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>13</v>
       </c>
@@ -6400,13 +6479,13 @@
         <v>26</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>13</v>
       </c>
@@ -6414,13 +6493,13 @@
         <v>26</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>13</v>
       </c>
@@ -6428,13 +6507,13 @@
         <v>26</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>13</v>
       </c>
@@ -6442,13 +6521,13 @@
         <v>26</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>13</v>
       </c>
@@ -6456,13 +6535,13 @@
         <v>26</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>13</v>
       </c>
@@ -6470,13 +6549,13 @@
         <v>26</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>13</v>
       </c>
@@ -6484,13 +6563,13 @@
         <v>26</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>13</v>
       </c>
@@ -6498,13 +6577,13 @@
         <v>26</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>13</v>
       </c>
@@ -6512,10 +6591,113 @@
         <v>26</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A378">
+        <v>12</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C378" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D378" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A379">
+        <v>12</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C379" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D379" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A380">
+        <v>12</v>
+      </c>
+      <c r="B380" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C380" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D380" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8580FB40-AF83-4070-ACE8-F0DE4922E674}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="115.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>46283</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>46288</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
